--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Customer Experience Analyst</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
@@ -1728,52 +1728,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, DynamoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=d57b1b89bb859a0c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Data Analyst, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>HighJump Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=09e31f46382738bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,77 +2831,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,87 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, DynamoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57b1b89bb859a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, DynamoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d57b1b89bb859a0c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst, Applications Engineering &amp; Manufacturing</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HighJump Consultant</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09e31f46382738bf</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>HighJump Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=09e31f46382738bf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,77 +2831,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,85 +3461,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,69 +2061,69 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, DynamoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57b1b89bb859a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HighJump Consultant</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09e31f46382738bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,15 +3461,50 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,69 +2061,69 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azure DBX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
@@ -1173,20 +1173,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,129 +2806,129 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,146 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Streaming</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>The Coca-Cola Company</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AI/ML Architect</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Avilamb</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,139 +2656,139 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3260,111 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI/ML Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Avilamb</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3155,111 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI/ML Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Avilamb</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,77 +2516,77 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3085,76 +3085,6 @@
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>Glue, EMR, Kinesis, S3, SQS, IAM, RDS, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2beecd9e43cf9c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,94 +1756,94 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,111 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Cloud Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Gainwell Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake / Cortex</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,15 +2971,50 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Java Developer / Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
@@ -1553,35 +1553,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake / Cortex</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Architect – Snowflake / Cortex</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,69 +2481,69 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,15 +3006,50 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
@@ -1243,20 +1243,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,50 +1563,50 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,129 +1616,129 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake / Cortex</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2665,391 +2665,6 @@
         </is>
       </c>
       <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ellenwood, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Romulus, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer - Hybrid On-Site</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Engineer - Hybrid On-Site</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Merrimack, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Healthcare Imaging Solution Architect</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Business Efficiency Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Masco</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Livonia, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Cloud Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Gainwell Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Architect II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2560,111 +2560,6 @@
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Business Efficiency Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Java Developer / Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Developer / Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
@@ -1278,55 +1278,55 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,129 +1371,129 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2140,426 +2140,6 @@
         </is>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Happen Bank</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ellenwood, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Expeditors</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Romulus, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Healthcare Imaging Solution Architect</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Cloud Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Gainwell Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Business Efficiency Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure DBX</t>
+          <t>Java Developer / Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Developer / Architect</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,85 +1178,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1930,216 +1930,6 @@
         </is>
       </c>
       <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Healthcare Imaging Solution Architect</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Business Efficiency Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,85 +1073,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1790,146 +1790,6 @@
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Healthcare Imaging Solution Architect</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,70 +818,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214e99b1fcb26e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer (Front-End)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Applications Engineering &amp; Manufacturing</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d6877a915f6eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3efe464181cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chicago Financial Search</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,85 +1711,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>

--- a/results/job_matches_2026-08-08.xlsx
+++ b/results/job_matches_2026-08-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer with GCP experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Oak Street Health, part of CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c315c7bc9b7790</t>
+          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Data Engg with DQ Exp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Generative AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecaed8b17bc14581</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER, ORIS: System/Application Development</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047b0e575b8ecaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66a7736b0c53983</t>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518b3fdcc7659de5</t>
+          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Front-End)</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7864b183e80ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sunwest Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sunwest Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb98e8790adee1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Data Scientist Specialist - Customer Service</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Healthcare Imaging Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f10f5f5a35f3b67</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Lindblad Expeditions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576ee1e65e819b57</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1580,146 +1580,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lindblad Expeditions</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddd1a3c6c51faef</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=172daad3fc8a7f79</t>
         </is>
